--- a/Data_process/question_stats/question_statistics.xlsx
+++ b/Data_process/question_stats/question_statistics.xlsx
@@ -7,14 +7,16 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="基本统计" sheetId="1" r:id="rId1"/>
+    <sheet name="选项数量分布(按领域)" sheetId="2" r:id="rId2"/>
+    <sheet name="选项数量分布(按选项数)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>Metric</t>
   </si>
@@ -53,6 +55,135 @@
   </si>
   <si>
     <t>Answer Options Count</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Number of Options</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>百分比</t>
+  </si>
+  <si>
+    <t>2选项问题</t>
+  </si>
+  <si>
+    <t>3选项问题</t>
+  </si>
+  <si>
+    <t>4选项问题</t>
+  </si>
+  <si>
+    <t>5选项问题</t>
+  </si>
+  <si>
+    <t>6选项问题</t>
+  </si>
+  <si>
+    <t>7选项问题</t>
+  </si>
+  <si>
+    <t>8选项问题</t>
+  </si>
+  <si>
+    <t>9选项问题</t>
+  </si>
+  <si>
+    <t>10选项问题</t>
+  </si>
+  <si>
+    <t>11选项问题</t>
+  </si>
+  <si>
+    <t>12选项问题</t>
+  </si>
+  <si>
+    <t>13选项问题</t>
+  </si>
+  <si>
+    <t>14选项问题</t>
+  </si>
+  <si>
+    <t>15选项问题</t>
+  </si>
+  <si>
+    <t>16选项问题</t>
+  </si>
+  <si>
+    <t>17选项问题</t>
+  </si>
+  <si>
+    <t>18选项问题</t>
+  </si>
+  <si>
+    <t>20选项问题</t>
+  </si>
+  <si>
+    <t>21选项问题</t>
+  </si>
+  <si>
+    <t>27选项问题</t>
+  </si>
+  <si>
+    <t>29选项问题</t>
+  </si>
+  <si>
+    <t>49选项问题</t>
+  </si>
+  <si>
+    <t>各领域总计</t>
+  </si>
+  <si>
+    <t>1.23%</t>
+  </si>
+  <si>
+    <t>1.72%</t>
+  </si>
+  <si>
+    <t>16.32%</t>
+  </si>
+  <si>
+    <t>42.70%</t>
+  </si>
+  <si>
+    <t>11.90%</t>
+  </si>
+  <si>
+    <t>7.85%</t>
+  </si>
+  <si>
+    <t>2.33%</t>
+  </si>
+  <si>
+    <t>1.96%</t>
+  </si>
+  <si>
+    <t>2.58%</t>
+  </si>
+  <si>
+    <t>2.70%</t>
+  </si>
+  <si>
+    <t>2.09%</t>
+  </si>
+  <si>
+    <t>0.61%</t>
+  </si>
+  <si>
+    <t>0.37%</t>
+  </si>
+  <si>
+    <t>0.12%</t>
+  </si>
+  <si>
+    <t>0.25%</t>
+  </si>
+  <si>
+    <t>100.00%</t>
   </si>
 </sst>
 </file>
@@ -521,4 +652,1917 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>38</v>
+      </c>
+      <c r="D5">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5">
+        <v>36</v>
+      </c>
+      <c r="G5">
+        <v>45</v>
+      </c>
+      <c r="H5">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="1">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="1">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="1">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="1">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="1">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="1">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="1">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="1">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="1">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="1">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1">
+        <v>49</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24">
+        <v>68</v>
+      </c>
+      <c r="C24">
+        <v>58</v>
+      </c>
+      <c r="D24">
+        <v>77</v>
+      </c>
+      <c r="E24">
+        <v>69</v>
+      </c>
+      <c r="F24">
+        <v>74</v>
+      </c>
+      <c r="G24">
+        <v>178</v>
+      </c>
+      <c r="H24">
+        <v>66</v>
+      </c>
+      <c r="I24">
+        <v>63</v>
+      </c>
+      <c r="J24">
+        <v>67</v>
+      </c>
+      <c r="K24">
+        <v>95</v>
+      </c>
+      <c r="L24">
+        <v>815</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>133</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>38</v>
+      </c>
+      <c r="D5">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5">
+        <v>36</v>
+      </c>
+      <c r="G5">
+        <v>45</v>
+      </c>
+      <c r="H5">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>348</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <v>97</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>64</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>17</v>
+      </c>
+      <c r="M13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>17</v>
+      </c>
+      <c r="M14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24">
+        <v>68</v>
+      </c>
+      <c r="C24">
+        <v>58</v>
+      </c>
+      <c r="D24">
+        <v>77</v>
+      </c>
+      <c r="E24">
+        <v>69</v>
+      </c>
+      <c r="F24">
+        <v>74</v>
+      </c>
+      <c r="G24">
+        <v>178</v>
+      </c>
+      <c r="H24">
+        <v>66</v>
+      </c>
+      <c r="I24">
+        <v>63</v>
+      </c>
+      <c r="J24">
+        <v>67</v>
+      </c>
+      <c r="K24">
+        <v>95</v>
+      </c>
+      <c r="L24">
+        <v>815</v>
+      </c>
+      <c r="M24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>